--- a/results/benchmark_results.xlsx
+++ b/results/benchmark_results.xlsx
@@ -445,7 +445,7 @@
         <v>0.0205</v>
       </c>
       <c r="C2" t="n">
-        <v>556.1</v>
+        <v>2224.1</v>
       </c>
     </row>
     <row r="3">
@@ -458,7 +458,7 @@
         <v>0.0389</v>
       </c>
       <c r="C3" t="n">
-        <v>862.7</v>
+        <v>3450.8</v>
       </c>
     </row>
     <row r="4">
@@ -468,10 +468,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2308</v>
+        <v>0.2303</v>
       </c>
       <c r="C4" t="n">
-        <v>581.5</v>
+        <v>2330.9</v>
       </c>
     </row>
     <row r="5">
@@ -481,10 +481,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.7075</v>
+        <v>2.7073</v>
       </c>
       <c r="C5" t="n">
-        <v>396.6</v>
+        <v>1586.5</v>
       </c>
     </row>
   </sheetData>
@@ -541,7 +541,7 @@
         <v>0.008200000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>4097.5</v>
+        <v>4097.2</v>
       </c>
     </row>
     <row r="4">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.073</v>
+        <v>0.0725</v>
       </c>
       <c r="C4" t="n">
-        <v>1838.9</v>
+        <v>1852.5</v>
       </c>
     </row>
     <row r="5">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7007</v>
+        <v>0.7004</v>
       </c>
       <c r="C5" t="n">
-        <v>1532.5</v>
+        <v>1533.1</v>
       </c>
     </row>
   </sheetData>
@@ -618,16 +618,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0102</v>
+        <v>0.0188</v>
       </c>
       <c r="C2" t="n">
-        <v>1122.1</v>
+        <v>605</v>
       </c>
       <c r="D2" t="n">
-        <v>2.02</v>
+        <v>1.09</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="3">
@@ -637,16 +637,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0077</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>4377.1</v>
+        <v>4254.4</v>
       </c>
       <c r="D3" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="E3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="4">
@@ -656,16 +656,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0716</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>1873.4</v>
+        <v>1877.6</v>
       </c>
       <c r="D4" t="n">
         <v>3.22</v>
       </c>
       <c r="E4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="5">
